--- a/education_forms/041_global_teaching_innovation_index_survey--education_forms.xlsx
+++ b/education_forms/041_global_teaching_innovation_index_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>innovation_in_english_language</t>
+          <t>innovation_in_english_language_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Innovation in English Language</t>
+          <t>Innovation In English Language 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>innovation_in_math</t>
+          <t>innovation_in_math_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Innovation in Math</t>
+          <t>Innovation In Math 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>innovation_in_science</t>
+          <t>innovation_in_science_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Innovation in Science</t>
+          <t>Innovation In Science 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>innovation_in_social_sciences</t>
+          <t>innovation_in_social_sciences_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Innovation in Social Sciences</t>
+          <t>Innovation In Social Sciences 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1227,7 +1227,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>innovation_in_english_language_choices</t>
+          <t>innovation_in_english_language_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>innovation_in_english_language_choices</t>
+          <t>innovation_in_english_language_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>innovation_in_english_language_choices</t>
+          <t>innovation_in_english_language_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>innovation_in_math_choices</t>
+          <t>innovation_in_math_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>innovation_in_math_choices</t>
+          <t>innovation_in_math_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>innovation_in_math_choices</t>
+          <t>innovation_in_math_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>innovation_in_science_choices</t>
+          <t>innovation_in_science_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1346,7 +1346,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>innovation_in_science_choices</t>
+          <t>innovation_in_science_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>innovation_in_science_choices</t>
+          <t>innovation_in_science_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>innovation_in_social_sciences_choices</t>
+          <t>innovation_in_social_sciences_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>innovation_in_social_sciences_choices</t>
+          <t>innovation_in_social_sciences_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1414,7 +1414,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>innovation_in_social_sciences_choices</t>
+          <t>innovation_in_social_sciences_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
